--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>126779021</v>
       </c>
       <c r="B5" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>126779020</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>126779021</v>
       </c>
       <c r="B5" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>126779020</v>
       </c>
       <c r="B6" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>126779021</v>
       </c>
       <c r="B5" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>126779020</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>126779021</v>
       </c>
       <c r="B5" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>126779020</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1227,6 +1227,2364 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127675595</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>869339</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7455036</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127675601</v>
+      </c>
+      <c r="B8" t="n">
+        <v>12357</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>101283</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Djupsvart brunbagge</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Melandrya dubia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaller, 1783)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>869352</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7454893</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Björkhögstubbe 1 med kläckhål och larvgång. Bilderna granskade av Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127675571</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>869543</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7454749</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127675591</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>869269</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7455027</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127675583</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>869380</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7454874</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127675551</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>869373</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7455036</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127675572</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>869549</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7454676</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127675592</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>869298</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7455041</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127675600</v>
+      </c>
+      <c r="B15" t="n">
+        <v>12357</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>101283</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Djupsvart brunbagge</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Melandrya dubia</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schaller, 1783)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>869339</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7454866</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Björkhögstubbe 2 med kläckhål och larvgång. Bilderna granskade av Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127675589</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>869249</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7454996</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127675566</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>869375</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7455037</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127675554</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97325</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>869367</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7454896</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127675573</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>869540</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7454662</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127675584</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>869399</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7454909</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127675562</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>869320</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7455042</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127675588</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>869240</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7454978</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127675586</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>869209</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7454935</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127675590</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>869241</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7455017</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127675587</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>869213</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7454943</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127675594</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>869338</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7455061</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127675596</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>869358</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7455041</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127675553</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91626</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>658</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>869366</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7454890</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127675567</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>869392</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7455024</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127675570</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>869574</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7454777</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -2117,7 +2117,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127675589</v>
+        <v>127675566</v>
       </c>
       <c r="B16" t="n">
         <v>79018</v>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>869249</v>
+        <v>869375</v>
       </c>
       <c r="R16" t="n">
-        <v>7454996</v>
+        <v>7455037</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2188,6 +2188,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2214,7 +2219,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127675566</v>
+        <v>127675589</v>
       </c>
       <c r="B17" t="n">
         <v>79018</v>
@@ -2249,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>869375</v>
+        <v>869249</v>
       </c>
       <c r="R17" t="n">
-        <v>7455037</v>
+        <v>7454996</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2285,11 +2290,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2607,10 +2607,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127675562</v>
+        <v>127675588</v>
       </c>
       <c r="B21" t="n">
-        <v>56844</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,21 +2618,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>869320</v>
+        <v>869240</v>
       </c>
       <c r="R21" t="n">
-        <v>7455042</v>
+        <v>7454978</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2678,11 +2678,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2709,10 +2704,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127675588</v>
+        <v>127675562</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>56844</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2720,21 +2715,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2744,10 +2739,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>869240</v>
+        <v>869320</v>
       </c>
       <c r="R22" t="n">
-        <v>7454978</v>
+        <v>7455042</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2780,6 +2775,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3194,10 +3194,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127675596</v>
+        <v>127675553</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>91626</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3205,21 +3205,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>869358</v>
+        <v>869366</v>
       </c>
       <c r="R27" t="n">
-        <v>7455041</v>
+        <v>7454890</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3291,10 +3291,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127675553</v>
+        <v>127675567</v>
       </c>
       <c r="B28" t="n">
-        <v>91626</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3302,21 +3302,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>869366</v>
+        <v>869392</v>
       </c>
       <c r="R28" t="n">
-        <v>7454890</v>
+        <v>7455024</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3362,6 +3362,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3388,7 +3393,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127675567</v>
+        <v>127675596</v>
       </c>
       <c r="B29" t="n">
         <v>79018</v>
@@ -3423,10 +3428,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>869392</v>
+        <v>869358</v>
       </c>
       <c r="R29" t="n">
-        <v>7455024</v>
+        <v>7455041</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3459,11 +3464,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1232,7 +1232,7 @@
         <v>127675595</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>127675571</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>127675591</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>127675583</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>127675572</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>127675592</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>127675566</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>127675589</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>127675554</v>
       </c>
       <c r="B18" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>127675573</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>127675584</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,10 +2607,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127675588</v>
+        <v>127675562</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>56846</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,21 +2618,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>869240</v>
+        <v>869320</v>
       </c>
       <c r="R21" t="n">
-        <v>7454978</v>
+        <v>7455042</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2678,6 +2678,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2704,10 +2709,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127675562</v>
+        <v>127675588</v>
       </c>
       <c r="B22" t="n">
-        <v>56844</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,21 +2720,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2739,10 +2744,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>869320</v>
+        <v>869240</v>
       </c>
       <c r="R22" t="n">
-        <v>7455042</v>
+        <v>7454978</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2775,11 +2780,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2809,7 +2809,7 @@
         <v>127675586</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>127675590</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>127675587</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>127675594</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3194,10 +3194,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127675553</v>
+        <v>127675567</v>
       </c>
       <c r="B27" t="n">
-        <v>91626</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3205,21 +3205,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>869366</v>
+        <v>869392</v>
       </c>
       <c r="R27" t="n">
-        <v>7454890</v>
+        <v>7455024</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3265,6 +3265,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3291,10 +3296,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127675567</v>
+        <v>127675596</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3326,10 +3331,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>869392</v>
+        <v>869358</v>
       </c>
       <c r="R28" t="n">
-        <v>7455024</v>
+        <v>7455041</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3362,11 +3367,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3393,10 +3393,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127675596</v>
+        <v>127675553</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>91628</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3404,21 +3404,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>869358</v>
+        <v>869366</v>
       </c>
       <c r="R29" t="n">
-        <v>7455041</v>
+        <v>7454890</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3493,7 +3493,7 @@
         <v>127675570</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3584,6 +3584,394 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127734306</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>869256</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7454794</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127734287</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>869277</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7454775</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127734305</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>869366</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7454824</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127734274</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Pahtalaki, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>869437</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7454624</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -2316,32 +2316,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127675554</v>
+        <v>127675573</v>
       </c>
       <c r="B18" t="n">
-        <v>97327</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>869367</v>
+        <v>869540</v>
       </c>
       <c r="R18" t="n">
-        <v>7454896</v>
+        <v>7454662</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2413,32 +2413,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127675573</v>
+        <v>127675554</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>97327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>869540</v>
+        <v>869367</v>
       </c>
       <c r="R19" t="n">
-        <v>7454662</v>
+        <v>7454896</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -3194,10 +3194,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127675567</v>
+        <v>127675553</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>91628</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3205,21 +3205,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>869392</v>
+        <v>869366</v>
       </c>
       <c r="R27" t="n">
-        <v>7455024</v>
+        <v>7454890</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3265,11 +3265,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3296,7 +3291,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127675596</v>
+        <v>127675567</v>
       </c>
       <c r="B28" t="n">
         <v>79020</v>
@@ -3331,10 +3326,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>869358</v>
+        <v>869392</v>
       </c>
       <c r="R28" t="n">
-        <v>7455041</v>
+        <v>7455024</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3367,6 +3362,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3393,10 +3393,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127675553</v>
+        <v>127675596</v>
       </c>
       <c r="B29" t="n">
-        <v>91628</v>
+        <v>79020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3404,21 +3404,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>869366</v>
+        <v>869358</v>
       </c>
       <c r="R29" t="n">
-        <v>7454890</v>
+        <v>7455041</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -2416,7 +2416,7 @@
         <v>127675554</v>
       </c>
       <c r="B19" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>127675553</v>
       </c>
       <c r="B27" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>127734287</v>
       </c>
       <c r="B32" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1232,7 +1232,7 @@
         <v>127675595</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127675571</v>
+        <v>127675591</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>869543</v>
+        <v>869269</v>
       </c>
       <c r="R9" t="n">
-        <v>7454749</v>
+        <v>7455027</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127675591</v>
+        <v>127675571</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>869269</v>
+        <v>869543</v>
       </c>
       <c r="R10" t="n">
-        <v>7455027</v>
+        <v>7454749</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1625,7 +1625,7 @@
         <v>127675583</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>127675572</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>127675592</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>127675566</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>127675589</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>127675573</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>127675554</v>
       </c>
       <c r="B19" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>127675584</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,10 +2607,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127675562</v>
+        <v>127675588</v>
       </c>
       <c r="B21" t="n">
-        <v>56846</v>
+        <v>79023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,21 +2618,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>869320</v>
+        <v>869240</v>
       </c>
       <c r="R21" t="n">
-        <v>7455042</v>
+        <v>7454978</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2678,11 +2678,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2709,10 +2704,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127675588</v>
+        <v>127675562</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>56849</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2720,21 +2715,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2744,10 +2739,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>869240</v>
+        <v>869320</v>
       </c>
       <c r="R22" t="n">
-        <v>7454978</v>
+        <v>7455042</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2780,6 +2775,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2809,7 +2809,7 @@
         <v>127675586</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>127675590</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3000,10 +3000,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127675587</v>
+        <v>127675594</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>869213</v>
+        <v>869338</v>
       </c>
       <c r="R25" t="n">
-        <v>7454943</v>
+        <v>7455061</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3097,10 +3097,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127675594</v>
+        <v>127675587</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>869338</v>
+        <v>869213</v>
       </c>
       <c r="R26" t="n">
-        <v>7455061</v>
+        <v>7454943</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3194,10 +3194,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127675553</v>
+        <v>127675567</v>
       </c>
       <c r="B27" t="n">
-        <v>91634</v>
+        <v>79023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3205,21 +3205,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>869366</v>
+        <v>869392</v>
       </c>
       <c r="R27" t="n">
-        <v>7454890</v>
+        <v>7455024</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3265,6 +3265,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3291,10 +3296,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127675567</v>
+        <v>127675596</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3326,10 +3331,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>869392</v>
+        <v>869358</v>
       </c>
       <c r="R28" t="n">
-        <v>7455024</v>
+        <v>7455041</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3362,11 +3367,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3393,10 +3393,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127675596</v>
+        <v>127675553</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>91637</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3404,21 +3404,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>869358</v>
+        <v>869366</v>
       </c>
       <c r="R29" t="n">
-        <v>7455041</v>
+        <v>7454890</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3493,7 +3493,7 @@
         <v>127675570</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>127734306</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>127734287</v>
       </c>
       <c r="B32" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>127734305</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>127734274</v>
       </c>
       <c r="B34" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1232,7 +1232,7 @@
         <v>127675595</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127675591</v>
+        <v>127675571</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>869269</v>
+        <v>869543</v>
       </c>
       <c r="R9" t="n">
-        <v>7455027</v>
+        <v>7454749</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127675571</v>
+        <v>127675591</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>869543</v>
+        <v>869269</v>
       </c>
       <c r="R10" t="n">
-        <v>7454749</v>
+        <v>7455027</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1625,7 +1625,7 @@
         <v>127675583</v>
       </c>
       <c r="B11" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>127675572</v>
       </c>
       <c r="B13" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>127675592</v>
       </c>
       <c r="B14" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>127675566</v>
       </c>
       <c r="B16" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>127675589</v>
       </c>
       <c r="B17" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>127675573</v>
       </c>
       <c r="B18" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>127675554</v>
       </c>
       <c r="B19" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>127675584</v>
       </c>
       <c r="B20" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>127675588</v>
       </c>
       <c r="B21" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>127675562</v>
       </c>
       <c r="B22" t="n">
-        <v>56849</v>
+        <v>56855</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>127675586</v>
       </c>
       <c r="B23" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>127675590</v>
       </c>
       <c r="B24" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3000,10 +3000,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127675594</v>
+        <v>127675587</v>
       </c>
       <c r="B25" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>869338</v>
+        <v>869213</v>
       </c>
       <c r="R25" t="n">
-        <v>7455061</v>
+        <v>7454943</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3097,10 +3097,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127675587</v>
+        <v>127675594</v>
       </c>
       <c r="B26" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>869213</v>
+        <v>869338</v>
       </c>
       <c r="R26" t="n">
-        <v>7454943</v>
+        <v>7455061</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3194,10 +3194,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127675567</v>
+        <v>127675553</v>
       </c>
       <c r="B27" t="n">
-        <v>79023</v>
+        <v>91645</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3205,21 +3205,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>869392</v>
+        <v>869366</v>
       </c>
       <c r="R27" t="n">
-        <v>7455024</v>
+        <v>7454890</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3265,11 +3265,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3296,10 +3291,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127675596</v>
+        <v>127675567</v>
       </c>
       <c r="B28" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,10 +3326,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>869358</v>
+        <v>869392</v>
       </c>
       <c r="R28" t="n">
-        <v>7455041</v>
+        <v>7455024</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3367,6 +3362,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3393,10 +3393,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127675553</v>
+        <v>127675596</v>
       </c>
       <c r="B29" t="n">
-        <v>91637</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3404,21 +3404,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>869366</v>
+        <v>869358</v>
       </c>
       <c r="R29" t="n">
-        <v>7454890</v>
+        <v>7455041</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3493,7 +3493,7 @@
         <v>127675570</v>
       </c>
       <c r="B30" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>127734306</v>
       </c>
       <c r="B31" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>127734287</v>
       </c>
       <c r="B32" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>127734305</v>
       </c>
       <c r="B33" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>127734274</v>
       </c>
       <c r="B34" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -2416,7 +2416,7 @@
         <v>127675554</v>
       </c>
       <c r="B19" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3194,10 +3194,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127675553</v>
+        <v>127675567</v>
       </c>
       <c r="B27" t="n">
-        <v>91645</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3205,21 +3205,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>869366</v>
+        <v>869392</v>
       </c>
       <c r="R27" t="n">
-        <v>7454890</v>
+        <v>7455024</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3265,6 +3265,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3291,7 +3296,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127675567</v>
+        <v>127675596</v>
       </c>
       <c r="B28" t="n">
         <v>79029</v>
@@ -3326,10 +3331,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>869392</v>
+        <v>869358</v>
       </c>
       <c r="R28" t="n">
-        <v>7455024</v>
+        <v>7455041</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3362,11 +3367,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3393,10 +3393,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127675596</v>
+        <v>127675553</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>91646</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3404,21 +3404,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>869358</v>
+        <v>869366</v>
       </c>
       <c r="R29" t="n">
-        <v>7455041</v>
+        <v>7454890</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3687,7 +3687,7 @@
         <v>127734287</v>
       </c>
       <c r="B32" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1622,32 +1622,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127675583</v>
+        <v>127675551</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>5197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>869380</v>
+        <v>869373</v>
       </c>
       <c r="R11" t="n">
-        <v>7454874</v>
+        <v>7455036</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1693,6 +1693,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,32 +1724,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127675551</v>
+        <v>127675583</v>
       </c>
       <c r="B12" t="n">
-        <v>5197</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>869373</v>
+        <v>869380</v>
       </c>
       <c r="R12" t="n">
-        <v>7455036</v>
+        <v>7454874</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1790,11 +1795,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2607,10 +2607,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127675588</v>
+        <v>127675562</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>56855</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,21 +2618,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>869240</v>
+        <v>869320</v>
       </c>
       <c r="R21" t="n">
-        <v>7454978</v>
+        <v>7455042</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2678,6 +2678,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2704,10 +2709,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127675562</v>
+        <v>127675588</v>
       </c>
       <c r="B22" t="n">
-        <v>56855</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,21 +2720,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2739,10 +2744,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>869320</v>
+        <v>869240</v>
       </c>
       <c r="R22" t="n">
-        <v>7455042</v>
+        <v>7454978</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2775,11 +2780,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3194,10 +3194,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127675567</v>
+        <v>127675553</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>91646</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3205,21 +3205,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>869392</v>
+        <v>869366</v>
       </c>
       <c r="R27" t="n">
-        <v>7455024</v>
+        <v>7454890</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3265,11 +3265,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3296,7 +3291,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127675596</v>
+        <v>127675567</v>
       </c>
       <c r="B28" t="n">
         <v>79029</v>
@@ -3331,10 +3326,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>869358</v>
+        <v>869392</v>
       </c>
       <c r="R28" t="n">
-        <v>7455041</v>
+        <v>7455024</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3367,6 +3362,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3393,10 +3393,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127675553</v>
+        <v>127675596</v>
       </c>
       <c r="B29" t="n">
-        <v>91646</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3404,21 +3404,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>869366</v>
+        <v>869358</v>
       </c>
       <c r="R29" t="n">
-        <v>7454890</v>
+        <v>7455041</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1622,32 +1622,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127675551</v>
+        <v>127675583</v>
       </c>
       <c r="B11" t="n">
-        <v>5197</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>869373</v>
+        <v>869380</v>
       </c>
       <c r="R11" t="n">
-        <v>7455036</v>
+        <v>7454874</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1693,11 +1693,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,32 +1719,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127675583</v>
+        <v>127675551</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>5197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1759,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>869380</v>
+        <v>869373</v>
       </c>
       <c r="R12" t="n">
-        <v>7454874</v>
+        <v>7455036</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1795,6 +1790,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2117,7 +2117,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127675566</v>
+        <v>127675589</v>
       </c>
       <c r="B16" t="n">
         <v>79029</v>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>869375</v>
+        <v>869249</v>
       </c>
       <c r="R16" t="n">
-        <v>7455037</v>
+        <v>7454996</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2188,11 +2188,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2219,7 +2214,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127675589</v>
+        <v>127675566</v>
       </c>
       <c r="B17" t="n">
         <v>79029</v>
@@ -2254,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>869249</v>
+        <v>869375</v>
       </c>
       <c r="R17" t="n">
-        <v>7454996</v>
+        <v>7455037</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2290,6 +2285,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2416,7 +2416,7 @@
         <v>127675554</v>
       </c>
       <c r="B19" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2607,10 +2607,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127675562</v>
+        <v>127675588</v>
       </c>
       <c r="B21" t="n">
-        <v>56855</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,21 +2618,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>869320</v>
+        <v>869240</v>
       </c>
       <c r="R21" t="n">
-        <v>7455042</v>
+        <v>7454978</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2678,11 +2678,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2709,10 +2704,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127675588</v>
+        <v>127675562</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>56855</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2720,21 +2715,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2744,10 +2739,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>869240</v>
+        <v>869320</v>
       </c>
       <c r="R22" t="n">
-        <v>7454978</v>
+        <v>7455042</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2780,6 +2775,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3000,7 +3000,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127675587</v>
+        <v>127675594</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>869213</v>
+        <v>869338</v>
       </c>
       <c r="R25" t="n">
-        <v>7454943</v>
+        <v>7455061</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3097,7 +3097,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127675594</v>
+        <v>127675587</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>869338</v>
+        <v>869213</v>
       </c>
       <c r="R26" t="n">
-        <v>7455061</v>
+        <v>7454943</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3194,10 +3194,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127675553</v>
+        <v>127675567</v>
       </c>
       <c r="B27" t="n">
-        <v>91646</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3205,21 +3205,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>869366</v>
+        <v>869392</v>
       </c>
       <c r="R27" t="n">
-        <v>7454890</v>
+        <v>7455024</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3265,6 +3265,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3291,7 +3296,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127675567</v>
+        <v>127675596</v>
       </c>
       <c r="B28" t="n">
         <v>79029</v>
@@ -3326,10 +3331,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>869392</v>
+        <v>869358</v>
       </c>
       <c r="R28" t="n">
-        <v>7455024</v>
+        <v>7455041</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3362,11 +3367,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3393,10 +3393,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127675596</v>
+        <v>127675553</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>91647</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3404,21 +3404,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>869358</v>
+        <v>869366</v>
       </c>
       <c r="R29" t="n">
-        <v>7455041</v>
+        <v>7454890</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3687,7 +3687,7 @@
         <v>127734287</v>
       </c>
       <c r="B32" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -2416,7 +2416,7 @@
         <v>127675554</v>
       </c>
       <c r="B19" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127675594</v>
+        <v>127675587</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>869338</v>
+        <v>869213</v>
       </c>
       <c r="R25" t="n">
-        <v>7455061</v>
+        <v>7454943</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3097,7 +3097,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127675587</v>
+        <v>127675594</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>869213</v>
+        <v>869338</v>
       </c>
       <c r="R26" t="n">
-        <v>7454943</v>
+        <v>7455061</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3194,10 +3194,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127675567</v>
+        <v>127675553</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>91648</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3205,21 +3205,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>869392</v>
+        <v>869366</v>
       </c>
       <c r="R27" t="n">
-        <v>7455024</v>
+        <v>7454890</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3265,11 +3265,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3296,7 +3291,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127675596</v>
+        <v>127675567</v>
       </c>
       <c r="B28" t="n">
         <v>79029</v>
@@ -3331,10 +3326,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>869358</v>
+        <v>869392</v>
       </c>
       <c r="R28" t="n">
-        <v>7455041</v>
+        <v>7455024</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3367,6 +3362,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3393,10 +3393,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127675553</v>
+        <v>127675596</v>
       </c>
       <c r="B29" t="n">
-        <v>91647</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3404,21 +3404,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>869366</v>
+        <v>869358</v>
       </c>
       <c r="R29" t="n">
-        <v>7454890</v>
+        <v>7455041</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3687,7 +3687,7 @@
         <v>127734287</v>
       </c>
       <c r="B32" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -2607,10 +2607,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127675588</v>
+        <v>127675562</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>56855</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,21 +2618,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>869240</v>
+        <v>869320</v>
       </c>
       <c r="R21" t="n">
-        <v>7454978</v>
+        <v>7455042</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2678,6 +2678,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2704,10 +2709,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127675562</v>
+        <v>127675588</v>
       </c>
       <c r="B22" t="n">
-        <v>56855</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,21 +2720,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2739,10 +2744,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>869320</v>
+        <v>869240</v>
       </c>
       <c r="R22" t="n">
-        <v>7455042</v>
+        <v>7454978</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2775,11 +2780,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3000,7 +3000,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127675587</v>
+        <v>127675594</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>869213</v>
+        <v>869338</v>
       </c>
       <c r="R25" t="n">
-        <v>7454943</v>
+        <v>7455061</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3097,7 +3097,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127675594</v>
+        <v>127675587</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>869338</v>
+        <v>869213</v>
       </c>
       <c r="R26" t="n">
-        <v>7455061</v>
+        <v>7454943</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -2316,32 +2316,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127675573</v>
+        <v>127675554</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>97347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>869540</v>
+        <v>869367</v>
       </c>
       <c r="R18" t="n">
-        <v>7454662</v>
+        <v>7454896</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2413,32 +2413,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127675554</v>
+        <v>127675573</v>
       </c>
       <c r="B19" t="n">
-        <v>97347</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>869367</v>
+        <v>869540</v>
       </c>
       <c r="R19" t="n">
-        <v>7454896</v>
+        <v>7454662</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1622,32 +1622,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127675583</v>
+        <v>127675551</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>5197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>869380</v>
+        <v>869373</v>
       </c>
       <c r="R11" t="n">
-        <v>7454874</v>
+        <v>7455036</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1693,6 +1693,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,32 +1724,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127675551</v>
+        <v>127675583</v>
       </c>
       <c r="B12" t="n">
-        <v>5197</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>869373</v>
+        <v>869380</v>
       </c>
       <c r="R12" t="n">
-        <v>7455036</v>
+        <v>7454874</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1790,11 +1795,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2607,10 +2607,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127675562</v>
+        <v>127675588</v>
       </c>
       <c r="B21" t="n">
-        <v>56855</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,21 +2618,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>869320</v>
+        <v>869240</v>
       </c>
       <c r="R21" t="n">
-        <v>7455042</v>
+        <v>7454978</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2678,11 +2678,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2709,10 +2704,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127675588</v>
+        <v>127675562</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>56855</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2720,21 +2715,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2744,10 +2739,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>869240</v>
+        <v>869320</v>
       </c>
       <c r="R22" t="n">
-        <v>7454978</v>
+        <v>7455042</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2780,6 +2775,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -2117,7 +2117,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127675589</v>
+        <v>127675566</v>
       </c>
       <c r="B16" t="n">
         <v>79029</v>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>869249</v>
+        <v>869375</v>
       </c>
       <c r="R16" t="n">
-        <v>7454996</v>
+        <v>7455037</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2188,6 +2188,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2214,7 +2219,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127675566</v>
+        <v>127675589</v>
       </c>
       <c r="B17" t="n">
         <v>79029</v>
@@ -2249,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>869375</v>
+        <v>869249</v>
       </c>
       <c r="R17" t="n">
-        <v>7455037</v>
+        <v>7454996</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2285,11 +2290,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2316,32 +2316,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127675554</v>
+        <v>127675573</v>
       </c>
       <c r="B18" t="n">
-        <v>97347</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>869367</v>
+        <v>869540</v>
       </c>
       <c r="R18" t="n">
-        <v>7454896</v>
+        <v>7454662</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2413,32 +2413,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127675573</v>
+        <v>127675554</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>97347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>869540</v>
+        <v>869367</v>
       </c>
       <c r="R19" t="n">
-        <v>7454662</v>
+        <v>7454896</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2607,10 +2607,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127675588</v>
+        <v>127675562</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>56855</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,21 +2618,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>869240</v>
+        <v>869320</v>
       </c>
       <c r="R21" t="n">
-        <v>7454978</v>
+        <v>7455042</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2678,6 +2678,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2704,10 +2709,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127675562</v>
+        <v>127675588</v>
       </c>
       <c r="B22" t="n">
-        <v>56855</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,21 +2720,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2739,10 +2744,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>869320</v>
+        <v>869240</v>
       </c>
       <c r="R22" t="n">
-        <v>7455042</v>
+        <v>7454978</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2775,11 +2780,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1622,32 +1622,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127675551</v>
+        <v>127675583</v>
       </c>
       <c r="B11" t="n">
-        <v>5197</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>869373</v>
+        <v>869380</v>
       </c>
       <c r="R11" t="n">
-        <v>7455036</v>
+        <v>7454874</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1693,11 +1693,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,32 +1719,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127675583</v>
+        <v>127675551</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>5197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1759,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>869380</v>
+        <v>869373</v>
       </c>
       <c r="R12" t="n">
-        <v>7454874</v>
+        <v>7455036</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1795,6 +1790,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2316,32 +2316,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127675573</v>
+        <v>127675554</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>97347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>869540</v>
+        <v>869367</v>
       </c>
       <c r="R18" t="n">
-        <v>7454662</v>
+        <v>7454896</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2413,32 +2413,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127675554</v>
+        <v>127675573</v>
       </c>
       <c r="B19" t="n">
-        <v>97347</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>869367</v>
+        <v>869540</v>
       </c>
       <c r="R19" t="n">
-        <v>7454896</v>
+        <v>7454662</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -2117,7 +2117,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127675566</v>
+        <v>127675589</v>
       </c>
       <c r="B16" t="n">
         <v>79029</v>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>869375</v>
+        <v>869249</v>
       </c>
       <c r="R16" t="n">
-        <v>7455037</v>
+        <v>7454996</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2188,11 +2188,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2219,7 +2214,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127675589</v>
+        <v>127675566</v>
       </c>
       <c r="B17" t="n">
         <v>79029</v>
@@ -2254,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>869249</v>
+        <v>869375</v>
       </c>
       <c r="R17" t="n">
-        <v>7454996</v>
+        <v>7455037</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2290,6 +2285,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2607,10 +2607,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127675562</v>
+        <v>127675588</v>
       </c>
       <c r="B21" t="n">
-        <v>56855</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,21 +2618,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>869320</v>
+        <v>869240</v>
       </c>
       <c r="R21" t="n">
-        <v>7455042</v>
+        <v>7454978</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2678,11 +2678,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2709,10 +2704,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127675588</v>
+        <v>127675562</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>56855</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2720,21 +2715,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2744,10 +2739,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>869240</v>
+        <v>869320</v>
       </c>
       <c r="R22" t="n">
-        <v>7454978</v>
+        <v>7455042</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2780,6 +2775,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1622,32 +1622,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127675583</v>
+        <v>127675551</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>5197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>869380</v>
+        <v>869373</v>
       </c>
       <c r="R11" t="n">
-        <v>7454874</v>
+        <v>7455036</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1693,6 +1693,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,32 +1724,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127675551</v>
+        <v>127675583</v>
       </c>
       <c r="B12" t="n">
-        <v>5197</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>869373</v>
+        <v>869380</v>
       </c>
       <c r="R12" t="n">
-        <v>7455036</v>
+        <v>7454874</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1790,11 +1795,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2117,7 +2117,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127675589</v>
+        <v>127675566</v>
       </c>
       <c r="B16" t="n">
         <v>79029</v>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>869249</v>
+        <v>869375</v>
       </c>
       <c r="R16" t="n">
-        <v>7454996</v>
+        <v>7455037</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2188,6 +2188,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2214,7 +2219,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127675566</v>
+        <v>127675589</v>
       </c>
       <c r="B17" t="n">
         <v>79029</v>
@@ -2249,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>869375</v>
+        <v>869249</v>
       </c>
       <c r="R17" t="n">
-        <v>7455037</v>
+        <v>7454996</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2285,11 +2290,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2316,32 +2316,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127675554</v>
+        <v>127675573</v>
       </c>
       <c r="B18" t="n">
-        <v>97347</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>869367</v>
+        <v>869540</v>
       </c>
       <c r="R18" t="n">
-        <v>7454896</v>
+        <v>7454662</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2413,32 +2413,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127675573</v>
+        <v>127675554</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>97347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>869540</v>
+        <v>869367</v>
       </c>
       <c r="R19" t="n">
-        <v>7454662</v>
+        <v>7454896</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1232,7 +1232,7 @@
         <v>127675595</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>127675571</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>127675591</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>127675583</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>127675572</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>127675592</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>127675566</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>127675589</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2316,32 +2316,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127675573</v>
+        <v>127675554</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>97355</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>869540</v>
+        <v>869367</v>
       </c>
       <c r="R18" t="n">
-        <v>7454662</v>
+        <v>7454896</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2413,32 +2413,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127675554</v>
+        <v>127675573</v>
       </c>
       <c r="B19" t="n">
-        <v>97347</v>
+        <v>79032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>869367</v>
+        <v>869540</v>
       </c>
       <c r="R19" t="n">
-        <v>7454896</v>
+        <v>7454662</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2513,7 +2513,7 @@
         <v>127675584</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         <v>127675588</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>127675586</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>127675590</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3000,10 +3000,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127675594</v>
+        <v>127675587</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>869338</v>
+        <v>869213</v>
       </c>
       <c r="R25" t="n">
-        <v>7455061</v>
+        <v>7454943</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3097,10 +3097,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127675587</v>
+        <v>127675594</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>869213</v>
+        <v>869338</v>
       </c>
       <c r="R26" t="n">
-        <v>7454943</v>
+        <v>7455061</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3194,10 +3194,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127675553</v>
+        <v>127675567</v>
       </c>
       <c r="B27" t="n">
-        <v>91648</v>
+        <v>79032</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3205,21 +3205,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>869366</v>
+        <v>869392</v>
       </c>
       <c r="R27" t="n">
-        <v>7454890</v>
+        <v>7455024</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3265,6 +3265,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3291,10 +3296,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127675567</v>
+        <v>127675596</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3326,10 +3331,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>869392</v>
+        <v>869358</v>
       </c>
       <c r="R28" t="n">
-        <v>7455024</v>
+        <v>7455041</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3362,11 +3367,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3393,10 +3393,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127675596</v>
+        <v>127675553</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>91656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3404,21 +3404,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>869358</v>
+        <v>869366</v>
       </c>
       <c r="R29" t="n">
-        <v>7455041</v>
+        <v>7454890</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3493,7 +3493,7 @@
         <v>127675570</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>127734306</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>127734287</v>
       </c>
       <c r="B32" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>127734305</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>127734274</v>
       </c>
       <c r="B34" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -3590,7 +3590,7 @@
         <v>127734306</v>
       </c>
       <c r="B31" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>127734287</v>
       </c>
       <c r="B32" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>127734305</v>
       </c>
       <c r="B33" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>127734274</v>
       </c>
       <c r="B34" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1010,7 +1010,7 @@
         <v>126779021</v>
       </c>
       <c r="B5" t="n">
-        <v>91348</v>
+        <v>91337</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>126779020</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1232,7 +1232,7 @@
         <v>127675595</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>79243</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,6 +1258,9 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -1308,6 +1311,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1322,14 +1326,18 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>127675601</v>
       </c>
       <c r="B8" t="n">
-        <v>12357</v>
+        <v>12359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,6 +1363,11 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -1410,6 +1423,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1424,14 +1438,18 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>127675571</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>79243</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1457,6 +1475,9 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -1507,6 +1528,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1521,14 +1543,18 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>127675591</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>79243</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,6 +1580,9 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -1604,6 +1633,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1618,7 +1648,11 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1727,7 +1761,7 @@
         <v>127675583</v>
       </c>
       <c r="B12" t="n">
-        <v>79032</v>
+        <v>79243</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,6 +1787,9 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -1803,6 +1840,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1817,14 +1855,18 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>127675572</v>
       </c>
       <c r="B13" t="n">
-        <v>79032</v>
+        <v>79243</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,6 +1892,9 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -1900,6 +1945,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1914,14 +1960,18 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>127675592</v>
       </c>
       <c r="B14" t="n">
-        <v>79032</v>
+        <v>79243</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1947,6 +1997,9 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -1997,6 +2050,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2011,14 +2065,18 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>127675600</v>
       </c>
       <c r="B15" t="n">
-        <v>12357</v>
+        <v>12359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2044,6 +2102,11 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -2099,6 +2162,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2113,14 +2177,18 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>127675566</v>
       </c>
       <c r="B16" t="n">
-        <v>79032</v>
+        <v>79243</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,6 +2214,9 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -2201,6 +2272,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2215,14 +2287,18 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>127675589</v>
       </c>
       <c r="B17" t="n">
-        <v>79032</v>
+        <v>79243</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2248,6 +2324,9 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -2298,6 +2377,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2312,7 +2392,11 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2416,7 +2500,7 @@
         <v>127675573</v>
       </c>
       <c r="B19" t="n">
-        <v>79032</v>
+        <v>79243</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2442,6 +2526,9 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -2492,6 +2579,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2506,14 +2594,18 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>127675584</v>
       </c>
       <c r="B20" t="n">
-        <v>79032</v>
+        <v>79243</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2539,6 +2631,9 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -2589,6 +2684,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2603,14 +2699,18 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>127675588</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>79243</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2636,6 +2736,9 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -2686,6 +2789,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2700,7 +2804,11 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2809,7 +2917,7 @@
         <v>127675586</v>
       </c>
       <c r="B23" t="n">
-        <v>79032</v>
+        <v>79243</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2835,6 +2943,9 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -2885,6 +2996,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2899,14 +3011,18 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>127675590</v>
       </c>
       <c r="B24" t="n">
-        <v>79032</v>
+        <v>79243</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2932,6 +3048,9 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -2982,6 +3101,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2996,14 +3116,18 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>127675587</v>
       </c>
       <c r="B25" t="n">
-        <v>79032</v>
+        <v>79243</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3029,6 +3153,9 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -3079,6 +3206,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3093,14 +3221,18 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>127675594</v>
       </c>
       <c r="B26" t="n">
-        <v>79032</v>
+        <v>79243</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3126,6 +3258,9 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -3176,6 +3311,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3190,14 +3326,18 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>127675567</v>
       </c>
       <c r="B27" t="n">
-        <v>79032</v>
+        <v>79243</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3223,6 +3363,9 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -3278,6 +3421,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3292,14 +3436,18 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>127675596</v>
       </c>
       <c r="B28" t="n">
-        <v>79032</v>
+        <v>79243</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3325,6 +3473,9 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -3375,6 +3526,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3389,14 +3541,18 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>127675553</v>
       </c>
       <c r="B29" t="n">
-        <v>91656</v>
+        <v>92106</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3413,15 +3569,18 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -3472,6 +3631,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3486,14 +3646,18 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>127675570</v>
       </c>
       <c r="B30" t="n">
-        <v>79032</v>
+        <v>79243</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3519,6 +3683,9 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -3569,6 +3736,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3583,14 +3751,18 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>127734306</v>
       </c>
       <c r="B31" t="n">
-        <v>79083</v>
+        <v>79243</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3616,6 +3788,9 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -3666,6 +3841,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3680,14 +3856,18 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>127734287</v>
       </c>
       <c r="B32" t="n">
-        <v>98571</v>
+        <v>99013</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3713,6 +3893,10 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -3763,6 +3947,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3777,14 +3962,18 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>127734305</v>
       </c>
       <c r="B33" t="n">
-        <v>79083</v>
+        <v>79243</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3810,6 +3999,9 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -3860,6 +4052,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3874,7 +4067,11 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -2815,7 +2815,7 @@
         <v>127675562</v>
       </c>
       <c r="B22" t="n">
-        <v>56855</v>
+        <v>57064</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,6 +2841,10 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -2910,7 +2914,11 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4078,7 +4086,7 @@
         <v>127734274</v>
       </c>
       <c r="B34" t="n">
-        <v>57845</v>
+        <v>58043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4104,6 +4112,10 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
@@ -4168,7 +4180,11 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1232,7 +1232,7 @@
         <v>127675595</v>
       </c>
       <c r="B7" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>127675571</v>
       </c>
       <c r="B9" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>127675591</v>
       </c>
       <c r="B10" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>127675583</v>
       </c>
       <c r="B12" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>127675572</v>
       </c>
       <c r="B13" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>127675592</v>
       </c>
       <c r="B14" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>127675566</v>
       </c>
       <c r="B16" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>127675589</v>
       </c>
       <c r="B17" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>127675573</v>
       </c>
       <c r="B19" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>127675584</v>
       </c>
       <c r="B20" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>127675588</v>
       </c>
       <c r="B21" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>127675586</v>
       </c>
       <c r="B23" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>127675590</v>
       </c>
       <c r="B24" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>127675587</v>
       </c>
       <c r="B25" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>127675594</v>
       </c>
       <c r="B26" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>127675567</v>
       </c>
       <c r="B27" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>127675596</v>
       </c>
       <c r="B28" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>127675553</v>
       </c>
       <c r="B29" t="n">
-        <v>92106</v>
+        <v>92107</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>127675570</v>
       </c>
       <c r="B30" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>127734306</v>
       </c>
       <c r="B31" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>127734287</v>
       </c>
       <c r="B32" t="n">
-        <v>99013</v>
+        <v>99014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>127734305</v>
       </c>
       <c r="B33" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1232,7 +1232,7 @@
         <v>127675595</v>
       </c>
       <c r="B7" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>127675571</v>
       </c>
       <c r="B9" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>127675591</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>127675583</v>
       </c>
       <c r="B12" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>127675572</v>
       </c>
       <c r="B13" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>127675592</v>
       </c>
       <c r="B14" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>127675566</v>
       </c>
       <c r="B16" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>127675589</v>
       </c>
       <c r="B17" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>127675573</v>
       </c>
       <c r="B19" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>127675584</v>
       </c>
       <c r="B20" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>127675588</v>
       </c>
       <c r="B21" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>127675586</v>
       </c>
       <c r="B23" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>127675590</v>
       </c>
       <c r="B24" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>127675587</v>
       </c>
       <c r="B25" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>127675594</v>
       </c>
       <c r="B26" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>127675567</v>
       </c>
       <c r="B27" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>127675596</v>
       </c>
       <c r="B28" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>127675553</v>
       </c>
       <c r="B29" t="n">
-        <v>92107</v>
+        <v>92108</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>127675570</v>
       </c>
       <c r="B30" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>127734306</v>
       </c>
       <c r="B31" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>127734287</v>
       </c>
       <c r="B32" t="n">
-        <v>99014</v>
+        <v>99015</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>127734305</v>
       </c>
       <c r="B33" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -3560,7 +3560,7 @@
         <v>127675553</v>
       </c>
       <c r="B29" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>127734287</v>
       </c>
       <c r="B32" t="n">
-        <v>99015</v>
+        <v>99018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1232,7 +1232,7 @@
         <v>127675595</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>127675571</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>127675591</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>127675583</v>
       </c>
       <c r="B12" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>127675572</v>
       </c>
       <c r="B13" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>127675592</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>127675566</v>
       </c>
       <c r="B16" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>127675589</v>
       </c>
       <c r="B17" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>127675573</v>
       </c>
       <c r="B19" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>127675584</v>
       </c>
       <c r="B20" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>127675588</v>
       </c>
       <c r="B21" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>127675586</v>
       </c>
       <c r="B23" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>127675590</v>
       </c>
       <c r="B24" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>127675587</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>127675594</v>
       </c>
       <c r="B26" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>127675567</v>
       </c>
       <c r="B27" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>127675596</v>
       </c>
       <c r="B28" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>127675553</v>
       </c>
       <c r="B29" t="n">
-        <v>92111</v>
+        <v>92112</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>127675570</v>
       </c>
       <c r="B30" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>127734306</v>
       </c>
       <c r="B31" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>127734287</v>
       </c>
       <c r="B32" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>127734305</v>
       </c>
       <c r="B33" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1232,7 +1232,7 @@
         <v>127675595</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>127675571</v>
       </c>
       <c r="B9" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>127675591</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>127675583</v>
       </c>
       <c r="B12" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>127675572</v>
       </c>
       <c r="B13" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>127675592</v>
       </c>
       <c r="B14" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>127675566</v>
       </c>
       <c r="B16" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>127675589</v>
       </c>
       <c r="B17" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>127675573</v>
       </c>
       <c r="B19" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>127675584</v>
       </c>
       <c r="B20" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>127675588</v>
       </c>
       <c r="B21" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>127675562</v>
       </c>
       <c r="B22" t="n">
-        <v>57064</v>
+        <v>57066</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>127675586</v>
       </c>
       <c r="B23" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>127675590</v>
       </c>
       <c r="B24" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>127675587</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>127675594</v>
       </c>
       <c r="B26" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>127675567</v>
       </c>
       <c r="B27" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>127675596</v>
       </c>
       <c r="B28" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>127675553</v>
       </c>
       <c r="B29" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>127675570</v>
       </c>
       <c r="B30" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>127734306</v>
       </c>
       <c r="B31" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>127734287</v>
       </c>
       <c r="B32" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>127734305</v>
       </c>
       <c r="B33" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>127734274</v>
       </c>
       <c r="B34" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1232,7 +1232,7 @@
         <v>127675595</v>
       </c>
       <c r="B7" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>127675571</v>
       </c>
       <c r="B9" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>127675591</v>
       </c>
       <c r="B10" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>127675583</v>
       </c>
       <c r="B12" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>127675572</v>
       </c>
       <c r="B13" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>127675592</v>
       </c>
       <c r="B14" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>127675566</v>
       </c>
       <c r="B16" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>127675589</v>
       </c>
       <c r="B17" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>127675573</v>
       </c>
       <c r="B19" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>127675584</v>
       </c>
       <c r="B20" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>127675588</v>
       </c>
       <c r="B21" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>127675562</v>
       </c>
       <c r="B22" t="n">
-        <v>57066</v>
+        <v>57067</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>127675586</v>
       </c>
       <c r="B23" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>127675590</v>
       </c>
       <c r="B24" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>127675587</v>
       </c>
       <c r="B25" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>127675594</v>
       </c>
       <c r="B26" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>127675567</v>
       </c>
       <c r="B27" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>127675596</v>
       </c>
       <c r="B28" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>127675553</v>
       </c>
       <c r="B29" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>127675570</v>
       </c>
       <c r="B30" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>127734306</v>
       </c>
       <c r="B31" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>127734287</v>
       </c>
       <c r="B32" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>127734305</v>
       </c>
       <c r="B33" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>127734274</v>
       </c>
       <c r="B34" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1232,7 +1232,7 @@
         <v>127675595</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>127675571</v>
       </c>
       <c r="B9" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>127675591</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>127675583</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>127675572</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>127675592</v>
       </c>
       <c r="B14" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>127675566</v>
       </c>
       <c r="B16" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>127675589</v>
       </c>
       <c r="B17" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>127675573</v>
       </c>
       <c r="B19" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>127675584</v>
       </c>
       <c r="B20" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>127675588</v>
       </c>
       <c r="B21" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>127675586</v>
       </c>
       <c r="B23" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>127675590</v>
       </c>
       <c r="B24" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>127675587</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>127675594</v>
       </c>
       <c r="B26" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>127675567</v>
       </c>
       <c r="B27" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>127675596</v>
       </c>
       <c r="B28" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>127675553</v>
       </c>
       <c r="B29" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>127675570</v>
       </c>
       <c r="B30" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>127734306</v>
       </c>
       <c r="B31" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>127734287</v>
       </c>
       <c r="B32" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>127734305</v>
       </c>
       <c r="B33" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>127734274</v>
       </c>
       <c r="B34" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1232,7 +1232,7 @@
         <v>127675595</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         <v>127675601</v>
       </c>
       <c r="B8" t="n">
-        <v>12359</v>
+        <v>12362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>127675571</v>
       </c>
       <c r="B9" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>127675591</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>127675583</v>
       </c>
       <c r="B12" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>127675572</v>
       </c>
       <c r="B13" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>127675592</v>
       </c>
       <c r="B14" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>127675600</v>
       </c>
       <c r="B15" t="n">
-        <v>12359</v>
+        <v>12362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>127675566</v>
       </c>
       <c r="B16" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>127675589</v>
       </c>
       <c r="B17" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>127675573</v>
       </c>
       <c r="B19" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>127675584</v>
       </c>
       <c r="B20" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>127675588</v>
       </c>
       <c r="B21" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>127675562</v>
       </c>
       <c r="B22" t="n">
-        <v>57067</v>
+        <v>57070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>127675586</v>
       </c>
       <c r="B23" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>127675590</v>
       </c>
       <c r="B24" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>127675587</v>
       </c>
       <c r="B25" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>127675594</v>
       </c>
       <c r="B26" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>127675567</v>
       </c>
       <c r="B27" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>127675596</v>
       </c>
       <c r="B28" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>127675553</v>
       </c>
       <c r="B29" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>127675570</v>
       </c>
       <c r="B30" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>127734306</v>
       </c>
       <c r="B31" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>127734287</v>
       </c>
       <c r="B32" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>127734305</v>
       </c>
       <c r="B33" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>127734274</v>
       </c>
       <c r="B34" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -1232,7 +1232,7 @@
         <v>127675595</v>
       </c>
       <c r="B7" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>127675571</v>
       </c>
       <c r="B9" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>127675591</v>
       </c>
       <c r="B10" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>127675583</v>
       </c>
       <c r="B12" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>127675572</v>
       </c>
       <c r="B13" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>127675592</v>
       </c>
       <c r="B14" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>127675566</v>
       </c>
       <c r="B16" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>127675589</v>
       </c>
       <c r="B17" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>127675573</v>
       </c>
       <c r="B19" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>127675584</v>
       </c>
       <c r="B20" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>127675588</v>
       </c>
       <c r="B21" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>127675562</v>
       </c>
       <c r="B22" t="n">
-        <v>57070</v>
+        <v>57071</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>127675586</v>
       </c>
       <c r="B23" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>127675590</v>
       </c>
       <c r="B24" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>127675587</v>
       </c>
       <c r="B25" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>127675594</v>
       </c>
       <c r="B26" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>127675567</v>
       </c>
       <c r="B27" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>127675596</v>
       </c>
       <c r="B28" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>127675553</v>
       </c>
       <c r="B29" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>127675570</v>
       </c>
       <c r="B30" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>127734306</v>
       </c>
       <c r="B31" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>127734287</v>
       </c>
       <c r="B32" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>127734305</v>
       </c>
       <c r="B33" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>127734274</v>
       </c>
       <c r="B34" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98310004</v>
+        <v>127675553</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ritalaki, Nb</t>
+          <t>Pahtalaki, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>869237.9495089971</v>
+        <v>869366</v>
       </c>
       <c r="R2" t="n">
-        <v>7455014.258160657</v>
+        <v>7454890</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-07-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-07-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,55 +757,55 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98310005</v>
+        <v>98310007</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>869301.8701897559</v>
+        <v>869207</v>
       </c>
       <c r="R3" t="n">
-        <v>7455027.785961331</v>
+        <v>7455032</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,19 +848,9 @@
           <t>2021-07-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-07-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,19 +877,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98310007</v>
+        <v>127675566</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -929,19 +906,22 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ritalaki, Nb</t>
+          <t>Pahtalaki, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>869207.6843930988</v>
+        <v>869375</v>
       </c>
       <c r="R4" t="n">
-        <v>7455032.665813412</v>
+        <v>7455037</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,22 +945,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-07-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-07-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,66 +964,74 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126779021</v>
+        <v>127675567</v>
       </c>
       <c r="B5" t="n">
-        <v>91348</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>869614</v>
+        <v>869392</v>
       </c>
       <c r="R5" t="n">
-        <v>7454735</v>
+        <v>7455024</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1072,22 +1055,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,18 +1074,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1118,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126779020</v>
+        <v>127675570</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,37 +1108,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>869547</v>
+        <v>869574</v>
       </c>
       <c r="R6" t="n">
-        <v>7454766</v>
+        <v>7454777</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,22 +1165,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,18 +1179,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1229,14 +1202,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127675595</v>
+        <v>127675571</v>
       </c>
       <c r="B7" t="n">
-        <v>79254</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1267,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>869339</v>
+        <v>869543</v>
       </c>
       <c r="R7" t="n">
-        <v>7455036</v>
+        <v>7454749</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1334,39 +1307,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127675601</v>
+        <v>127675572</v>
       </c>
       <c r="B8" t="n">
-        <v>12362</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101283</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1374,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>869352</v>
+        <v>869549</v>
       </c>
       <c r="R8" t="n">
-        <v>7454893</v>
+        <v>7454676</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1410,11 +1381,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Björkhögstubbe 1 med kläckhål och larvgång. Bilderna granskade av Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,14 +1412,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127675571</v>
+        <v>127675573</v>
       </c>
       <c r="B9" t="n">
-        <v>79254</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1484,10 +1450,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>869543</v>
+        <v>869540</v>
       </c>
       <c r="R9" t="n">
-        <v>7454749</v>
+        <v>7454662</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1551,14 +1517,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127675591</v>
+        <v>127675582</v>
       </c>
       <c r="B10" t="n">
-        <v>79254</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1589,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>869269</v>
+        <v>869383</v>
       </c>
       <c r="R10" t="n">
-        <v>7455027</v>
+        <v>7454531</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,45 +1622,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127675551</v>
+        <v>127675583</v>
       </c>
       <c r="B11" t="n">
-        <v>5197</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>869373</v>
+        <v>869380</v>
       </c>
       <c r="R11" t="n">
-        <v>7455036</v>
+        <v>7454874</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1729,17 +1698,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1754,18 +1719,22 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127675583</v>
+        <v>127675584</v>
       </c>
       <c r="B12" t="n">
-        <v>79254</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1796,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>869380</v>
+        <v>869399</v>
       </c>
       <c r="R12" t="n">
-        <v>7454874</v>
+        <v>7454909</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1863,14 +1832,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127675572</v>
+        <v>127675586</v>
       </c>
       <c r="B13" t="n">
-        <v>79254</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1901,10 +1870,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>869549</v>
+        <v>869209</v>
       </c>
       <c r="R13" t="n">
-        <v>7454676</v>
+        <v>7454935</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1968,14 +1937,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127675592</v>
+        <v>127675587</v>
       </c>
       <c r="B14" t="n">
-        <v>79254</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2006,10 +1975,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>869298</v>
+        <v>869213</v>
       </c>
       <c r="R14" t="n">
-        <v>7455041</v>
+        <v>7454943</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2073,39 +2042,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127675600</v>
+        <v>127675588</v>
       </c>
       <c r="B15" t="n">
-        <v>12362</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101283</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Djupsvart brunbagge</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Melandrya dubia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaller, 1783)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2113,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>869339</v>
+        <v>869240</v>
       </c>
       <c r="R15" t="n">
-        <v>7454866</v>
+        <v>7454978</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2149,11 +2116,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Björkhögstubbe 2 med kläckhål och larvgång. Bilderna granskade av Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2185,14 +2147,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127675566</v>
+        <v>127675589</v>
       </c>
       <c r="B16" t="n">
-        <v>79254</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2223,10 +2185,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>869375</v>
+        <v>869249</v>
       </c>
       <c r="R16" t="n">
-        <v>7455037</v>
+        <v>7454996</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2259,11 +2221,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,14 +2252,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127675589</v>
+        <v>127675590</v>
       </c>
       <c r="B17" t="n">
-        <v>79254</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2333,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>869249</v>
+        <v>869241</v>
       </c>
       <c r="R17" t="n">
-        <v>7454996</v>
+        <v>7455017</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2400,45 +2357,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127675554</v>
+        <v>127675591</v>
       </c>
       <c r="B18" t="n">
-        <v>97355</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>869367</v>
+        <v>869269</v>
       </c>
       <c r="R18" t="n">
-        <v>7454896</v>
+        <v>7455027</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2479,6 +2439,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2493,18 +2454,22 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127675573</v>
+        <v>127675592</v>
       </c>
       <c r="B19" t="n">
-        <v>79254</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2535,10 +2500,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>869540</v>
+        <v>869298</v>
       </c>
       <c r="R19" t="n">
-        <v>7454662</v>
+        <v>7455041</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2602,14 +2567,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127675584</v>
+        <v>127675594</v>
       </c>
       <c r="B20" t="n">
-        <v>79254</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2640,10 +2605,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>869399</v>
+        <v>869338</v>
       </c>
       <c r="R20" t="n">
-        <v>7454909</v>
+        <v>7455061</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2707,14 +2672,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127675588</v>
+        <v>127675595</v>
       </c>
       <c r="B21" t="n">
-        <v>79254</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2745,10 +2710,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>869240</v>
+        <v>869339</v>
       </c>
       <c r="R21" t="n">
-        <v>7454978</v>
+        <v>7455036</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2812,38 +2777,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127675562</v>
+        <v>127675596</v>
       </c>
       <c r="B22" t="n">
-        <v>57071</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2851,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>869320</v>
+        <v>869358</v>
       </c>
       <c r="R22" t="n">
-        <v>7455042</v>
+        <v>7455041</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2889,17 +2853,13 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Upprörd, varnande</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2922,14 +2882,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127675586</v>
+        <v>127734305</v>
       </c>
       <c r="B23" t="n">
-        <v>79254</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2960,10 +2920,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>869209</v>
+        <v>869366</v>
       </c>
       <c r="R23" t="n">
-        <v>7454935</v>
+        <v>7454824</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2990,12 +2950,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,14 +2987,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127675590</v>
+        <v>127734306</v>
       </c>
       <c r="B24" t="n">
-        <v>79254</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3065,10 +3025,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>869241</v>
+        <v>869256</v>
       </c>
       <c r="R24" t="n">
-        <v>7455017</v>
+        <v>7454794</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3095,12 +3055,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3132,51 +3092,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127675587</v>
+        <v>98310005</v>
       </c>
       <c r="B25" t="n">
-        <v>79254</v>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pahtalaki, Nb</t>
+          <t>Ritalaki, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>869213</v>
+        <v>869301</v>
       </c>
       <c r="R25" t="n">
-        <v>7454943</v>
+        <v>7455028</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3200,12 +3157,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2021-07-21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2021-07-21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3214,60 +3171,57 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127675594</v>
+        <v>127675600</v>
       </c>
       <c r="B26" t="n">
-        <v>79254</v>
+        <v>12364</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>101283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3275,10 +3229,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>869338</v>
+        <v>869339</v>
       </c>
       <c r="R26" t="n">
-        <v>7455061</v>
+        <v>7454866</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3311,6 +3265,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Björkhögstubbe 2 med kläckhål och larvgång. Bilderna granskade av Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3342,37 +3301,39 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127675567</v>
+        <v>127675601</v>
       </c>
       <c r="B27" t="n">
-        <v>79254</v>
+        <v>12364</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>101283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Djupsvart brunbagge</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Melandrya dubia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaller, 1783)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3380,10 +3341,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>869392</v>
+        <v>869352</v>
       </c>
       <c r="R27" t="n">
-        <v>7455024</v>
+        <v>7454893</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3420,7 +3381,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Björkhögstubbe 1 med kläckhål och larvgång. Bilderna granskade av Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3452,37 +3413,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127675596</v>
+        <v>127675562</v>
       </c>
       <c r="B28" t="n">
-        <v>79254</v>
+        <v>57132</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3490,10 +3452,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>869358</v>
+        <v>869320</v>
       </c>
       <c r="R28" t="n">
-        <v>7455041</v>
+        <v>7455042</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3528,13 +3490,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3557,10 +3523,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127675553</v>
+        <v>127734274</v>
       </c>
       <c r="B29" t="n">
-        <v>92120</v>
+        <v>58114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3568,26 +3534,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3595,10 +3562,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>869366</v>
+        <v>869437</v>
       </c>
       <c r="R29" t="n">
-        <v>7454890</v>
+        <v>7454624</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3625,12 +3592,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3639,7 +3606,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3662,48 +3628,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127675570</v>
+        <v>127675551</v>
       </c>
       <c r="B30" t="n">
-        <v>79254</v>
+        <v>5199</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>869574</v>
+        <v>869373</v>
       </c>
       <c r="R30" t="n">
-        <v>7454777</v>
+        <v>7455036</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3738,13 +3701,17 @@
           <t>2025-08-18</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3759,59 +3726,52 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127734306</v>
+        <v>126779020</v>
       </c>
       <c r="B31" t="n">
-        <v>79254</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>869256</v>
+        <v>869547</v>
       </c>
       <c r="R31" t="n">
-        <v>7454794</v>
+        <v>7454766</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3835,12 +3795,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3849,19 +3819,18 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3875,7 +3844,7 @@
         <v>127734287</v>
       </c>
       <c r="B32" t="n">
-        <v>99027</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3978,48 +3947,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127734305</v>
+        <v>127675554</v>
       </c>
       <c r="B33" t="n">
-        <v>79254</v>
+        <v>97983</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Pahtalaki, Nb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>869366</v>
+        <v>869367</v>
       </c>
       <c r="R33" t="n">
-        <v>7454824</v>
+        <v>7454896</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4046,12 +4012,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4060,7 +4026,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4075,60 +4040,48 @@
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127734274</v>
+        <v>98310004</v>
       </c>
       <c r="B34" t="n">
-        <v>58051</v>
+        <v>99038</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>223597</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Pahtalaki, Nb</t>
+          <t>Ritalaki, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>869437</v>
+        <v>869238</v>
       </c>
       <c r="R34" t="n">
-        <v>7454624</v>
+        <v>7455014</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4152,12 +4105,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2021-07-21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2021-07-21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4172,15 +4125,630 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128145062</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Korkeakuusikko, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>870382</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7454846</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128145068</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Korkeakuusikko, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>870298</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7454974</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128145070</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Korkeakuusikko, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>870081</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7455254</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128145079</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Korkeakuusikko, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>870254</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7455025</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128145021</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Korkeakuusikko, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>870165</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7455129</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128145023</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Korkeakuusikko, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>870353</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7454896</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
         <is>
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>

--- a/artfynd/A 1571-2024 artfynd.xlsx
+++ b/artfynd/A 1571-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675553</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98310007</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675566</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675567</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675570</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675571</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675572</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1514,6 +1554,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675573</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1619,6 +1664,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675582</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1724,6 +1774,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675583</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1884,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675584</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1934,6 +1994,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675586</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2039,6 +2104,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675587</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2144,6 +2214,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675588</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2249,6 +2324,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675589</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2354,6 +2434,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675590</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2459,6 +2544,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675591</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2564,6 +2654,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675592</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2669,6 +2764,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675594</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2774,6 +2874,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675595</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2879,6 +2984,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675596</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2984,6 +3094,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127734305</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3089,6 +3204,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127734306</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3186,6 +3306,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98310005</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3298,6 +3423,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675600</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3410,6 +3540,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675601</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3520,6 +3655,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675562</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3625,6 +3765,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127734274</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3727,6 +3872,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675551</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3836,6 +3986,11 @@
       <c r="AY31" t="inlineStr">
         <is>
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126779020</t>
         </is>
       </c>
     </row>
@@ -3944,6 +4099,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127734287</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4041,6 +4201,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127675554</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4134,6 +4299,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98310004</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4239,6 +4409,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128145062</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4344,6 +4519,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128145068</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4449,6 +4629,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128145070</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4546,6 +4731,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128145079</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4643,6 +4833,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128145021</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4753,8 +4948,54 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128145023</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>